--- a/mistral_translate_work/split_by_prompt/excel/quest/lang_questtype/lang_questtype__quest__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/quest/lang_questtype/lang_questtype__quest__part_0001.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Chuyện Chưa Kể</t>
+          <t>Chuyện Bên Lề Chưa Kể</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chuyện Chưa Kể</t>
+          <t>Chuyện Bên Lề Chưa Kể</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Bản Ghi Đơn</t>
+          <t>Kỷ Lục Solo</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Bản Ghi Đơn</t>
+          <t>Kỷ Lục Solo</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ General</t>
+          <t>Nhiệm vụ chung</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ General</t>
+          <t>Nhiệm vụ chung</t>
         </is>
       </c>
     </row>
